--- a/data/trending_integrated_20260909_14.xlsx
+++ b/data/trending_integrated_20260909_14.xlsx
@@ -578,13 +578,13 @@
         <v>-1.06</v>
       </c>
       <c r="E2" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="F2" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G2" t="n">
-        <v>1440</v>
+        <v>1502</v>
       </c>
       <c r="H2" t="n">
         <v>0.77</v>
@@ -610,7 +610,7 @@
         <v>1.83</v>
       </c>
       <c r="O2" t="n">
-        <v>29692625055</v>
+        <v>29712696155</v>
       </c>
       <c r="P2" t="n">
         <v>21500</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미 FDA 2A상 승인 및 병용 요법 연구 결과 발표 등 긍정적인 뉴스가 다수 확인됨. 특히 다락손라십 대비 우수하다는 비교 결과와 암세포 사멸 효과에 대한 기대감이 높으며, 이를 바탕으로 주가 상승 및 상한가 가능성이 언급됨.</t>
+          <t>FDA 2A상 승인 및 암세포 사멸 관련 획기적 약물 뉴스.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['FDA', '암치료제', '연구 결과']</t>
+          <t>['FDA 2A상', '암세포 사멸', '다락손라십']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>-0.08</v>
       </c>
       <c r="E3" t="n">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="F3" t="n">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="G3" t="n">
-        <v>334</v>
+        <v>386</v>
       </c>
       <c r="H3" t="n">
         <v>0.36</v>
@@ -702,7 +702,7 @@
         <v>0.44</v>
       </c>
       <c r="O3" t="n">
-        <v>231191124165</v>
+        <v>232621844225</v>
       </c>
       <c r="P3" t="n">
         <v>20850</v>
@@ -711,23 +711,23 @@
         <v>4020</v>
       </c>
       <c r="R3" t="n">
-        <v>4000</v>
+        <v>10000</v>
       </c>
       <c r="S3" t="n">
         <v>19000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 SMR 관련주 폭등에 따른 기대감 속 거래량 부족 및 주포 자금력 의문. 12000원 돌파 시 추가 상승 전망.</t>
+          <t>미국 SMR 및 가스터빈 관련주 폭등 수혜 기대. 80% 품절주 및 정부 대미 투자 1호 관련 긍정적 전망.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['SMR', '주포', '가스터빈']</t>
+          <t>['SMR', '가스터빈', '품절주']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -762,13 +762,13 @@
         <v>0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F4" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G4" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="H4" t="n">
         <v>2.46</v>
@@ -794,7 +794,7 @@
         <v>2.45</v>
       </c>
       <c r="O4" t="n">
-        <v>37821456075</v>
+        <v>37855311285</v>
       </c>
       <c r="P4" t="n">
         <v>16200</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13950</v>
+        <v>13700</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+18.12%</t>
+          <t>+16.00%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.22</v>
       </c>
       <c r="E5" t="n">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="F5" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="G5" t="n">
-        <v>1341</v>
+        <v>1426</v>
       </c>
       <c r="H5" t="n">
         <v>5.64</v>
@@ -886,7 +886,7 @@
         <v>5.42</v>
       </c>
       <c r="O5" t="n">
-        <v>461562890735</v>
+        <v>468995254055</v>
       </c>
       <c r="P5" t="n">
         <v>30200</v>
@@ -895,10 +895,10 @@
         <v>3540</v>
       </c>
       <c r="R5" t="n">
-        <v>294000</v>
+        <v>392000</v>
       </c>
       <c r="S5" t="n">
-        <v>73000</v>
+        <v>82000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -931,79 +931,79 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>써니전자</t>
+          <t>현대바이오</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2525</v>
+        <v>7160</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+16.90%</t>
+          <t>+14.38%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.23</v>
+        <v>0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>103</v>
+        <v>209</v>
       </c>
       <c r="F6" t="n">
-        <v>53</v>
+        <v>108</v>
       </c>
       <c r="G6" t="n">
-        <v>201</v>
+        <v>1184</v>
       </c>
       <c r="H6" t="n">
-        <v>5.26</v>
+        <v>7.4</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>2160</v>
+        <v>6260</v>
       </c>
       <c r="K6" t="n">
-        <v>2200</v>
+        <v>6200</v>
       </c>
       <c r="L6" t="n">
-        <v>2705</v>
+        <v>7730</v>
       </c>
       <c r="M6" t="n">
-        <v>2200</v>
+        <v>6140</v>
       </c>
       <c r="N6" t="n">
-        <v>5.49</v>
+        <v>7.35</v>
       </c>
       <c r="O6" t="n">
-        <v>33277793878</v>
+        <v>68989792020</v>
       </c>
       <c r="P6" t="n">
-        <v>2705</v>
+        <v>21500</v>
       </c>
       <c r="Q6" t="n">
-        <v>1418</v>
+        <v>4565</v>
       </c>
       <c r="R6" t="n">
-        <v>-166000</v>
+        <v>-471000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>경영권 분쟁 및 지분 싸움 가능성, 엔비디아 관련 루머 및 단기 과열 언급.</t>
+          <t>뎅기열 중간 발표 및 오가노이드 실험 결과에 대한 기대감. 다락손라십 췌장암 치료제 및 페니트리움 항암 치료제 개발 진행.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['지분싸움', '엔비디아', '경영권']</t>
+          <t>['뎅기열', '오가노이드', '항암 치료제']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1011,91 +1011,91 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>004770</t>
+          <t>048410</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>현대바이오</t>
+          <t>써니전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7210</v>
+        <v>2430</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+15.18%</t>
+          <t>+12.50%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.05</v>
+        <v>-0.23</v>
       </c>
       <c r="E7" t="n">
-        <v>200</v>
+        <v>111</v>
       </c>
       <c r="F7" t="n">
-        <v>108</v>
+        <v>58</v>
       </c>
       <c r="G7" t="n">
-        <v>1127</v>
+        <v>240</v>
       </c>
       <c r="H7" t="n">
-        <v>7.4</v>
+        <v>5.26</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>6260</v>
+        <v>2160</v>
       </c>
       <c r="K7" t="n">
-        <v>6200</v>
+        <v>2200</v>
       </c>
       <c r="L7" t="n">
-        <v>7730</v>
+        <v>2705</v>
       </c>
       <c r="M7" t="n">
-        <v>6140</v>
+        <v>2200</v>
       </c>
       <c r="N7" t="n">
-        <v>7.35</v>
+        <v>5.49</v>
       </c>
       <c r="O7" t="n">
-        <v>68323496895</v>
+        <v>36615516621</v>
       </c>
       <c r="P7" t="n">
-        <v>21500</v>
+        <v>2705</v>
       </c>
       <c r="Q7" t="n">
-        <v>4565</v>
+        <v>1418</v>
       </c>
       <c r="R7" t="n">
-        <v>-509000</v>
+        <v>22000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>페니트리움바이오 관련 긍정적 데이터 발표 기대감. 공매도 세력과의 주가 방어 및 거래량 증가.</t>
+          <t>경영권 분쟁 및 지분 싸움 가능성, 엔비디아 관련 루머 및 단기 과열 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['페니트리움바이오', '공매도', '항암치료제']</t>
+          <t>['지분싸움', '엔비디아', '경영권']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>048410</t>
+          <t>004770</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>54100</v>
+        <v>53300</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+9.85%</t>
+          <t>+8.22%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.03</v>
       </c>
       <c r="E8" t="n">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="F8" t="n">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="G8" t="n">
-        <v>543</v>
+        <v>579</v>
       </c>
       <c r="H8" t="n">
         <v>14.96</v>
@@ -1162,7 +1162,7 @@
         <v>14.93</v>
       </c>
       <c r="O8" t="n">
-        <v>157198226750</v>
+        <v>160999870450</v>
       </c>
       <c r="P8" t="n">
         <v>108900</v>
@@ -1171,23 +1171,23 @@
         <v>18230</v>
       </c>
       <c r="R8" t="n">
-        <v>-220000</v>
+        <v>-215000</v>
       </c>
       <c r="S8" t="n">
-        <v>135000</v>
+        <v>154000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2분기 영업이익 적자에도 불구하고 높은 목표가 제시. 외인 매도세 속 기관 매수 기대.</t>
+          <t>수주 확정 및 2분기 영업이익 악화에도 불구하고 향후 매출 성장성 및 목표 주가 상향 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['영업이익', '목표가', '기관매수']</t>
+          <t>['수주 확정', '매출 성장성', '목표 주가']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14800</v>
+        <v>14730</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+8.03%</t>
+          <t>+7.52%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.39</v>
       </c>
       <c r="E9" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F9" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G9" t="n">
-        <v>1327</v>
+        <v>1368</v>
       </c>
       <c r="H9" t="n">
         <v>1.55</v>
@@ -1254,7 +1254,7 @@
         <v>1.94</v>
       </c>
       <c r="O9" t="n">
-        <v>416488535615</v>
+        <v>422097736005</v>
       </c>
       <c r="P9" t="n">
         <v>31500</v>
@@ -1263,23 +1263,23 @@
         <v>1252</v>
       </c>
       <c r="R9" t="n">
-        <v>488000</v>
+        <v>590000</v>
       </c>
       <c r="S9" t="n">
         <v>20000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>단기 박스권 돌파 및 상승 추세 전망. 차트 분석 기반 가격 상승 기대.</t>
+          <t>단기 박스권 돌파 및 2만 원 목표, 긍정적 차트 분석.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['차트 분석', '상승 추세', '단기 박스권']</t>
+          <t>['박스권 돌파', '차트 분석', '우상향']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,83 +1299,83 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6750</v>
+        <v>31550</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+4.98%</t>
+          <t>+6.05%</t>
         </is>
       </c>
       <c r="D10" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>655</v>
+      </c>
+      <c r="F10" t="n">
+        <v>241</v>
+      </c>
+      <c r="G10" t="n">
+        <v>914</v>
+      </c>
+      <c r="H10" t="n">
         <v>0.31</v>
       </c>
-      <c r="E10" t="n">
-        <v>345</v>
-      </c>
-      <c r="F10" t="n">
-        <v>159</v>
-      </c>
-      <c r="G10" t="n">
-        <v>512</v>
-      </c>
-      <c r="H10" t="n">
-        <v>16.71</v>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>6430</v>
+        <v>29750</v>
       </c>
       <c r="K10" t="n">
-        <v>6400</v>
+        <v>31600</v>
       </c>
       <c r="L10" t="n">
-        <v>7470</v>
+        <v>34200</v>
       </c>
       <c r="M10" t="n">
-        <v>6250</v>
+        <v>28300</v>
       </c>
       <c r="N10" t="n">
-        <v>16.4</v>
+        <v>0.23</v>
       </c>
       <c r="O10" t="n">
-        <v>97249601370</v>
+        <v>481347456925</v>
       </c>
       <c r="P10" t="n">
-        <v>13000</v>
+        <v>39350</v>
       </c>
       <c r="Q10" t="n">
-        <v>6030</v>
+        <v>8200</v>
       </c>
       <c r="R10" t="n">
-        <v>-684000</v>
+        <v>-1000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>주가 폭락 가능성과 600억 배당의 상반된 평가. 공매도 세력과의 주가 방어 시도.</t>
+          <t>혈압 반지에 대한 유럽 진출 뉴스 및 2차 파동 전망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['배당', '공매도', '주주환원']</t>
+          <t>['혈압 반지', '유럽 진출', '2차 파동']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,99 +1384,99 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0220W0</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>서산</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7980</v>
+        <v>6780</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+3.91%</t>
+          <t>+5.44%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.4</v>
+        <v>0.31</v>
       </c>
       <c r="E11" t="n">
-        <v>112</v>
+        <v>344</v>
       </c>
       <c r="F11" t="n">
-        <v>72</v>
+        <v>156</v>
       </c>
       <c r="G11" t="n">
-        <v>323</v>
+        <v>538</v>
       </c>
       <c r="H11" t="n">
-        <v>1.81</v>
+        <v>16.71</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>7680</v>
+        <v>6430</v>
       </c>
       <c r="K11" t="n">
-        <v>7780</v>
+        <v>6400</v>
       </c>
       <c r="L11" t="n">
-        <v>9000</v>
+        <v>7470</v>
       </c>
       <c r="M11" t="n">
-        <v>7750</v>
+        <v>6250</v>
       </c>
       <c r="N11" t="n">
-        <v>0.41</v>
+        <v>16.4</v>
       </c>
       <c r="O11" t="n">
-        <v>112939264480</v>
+        <v>98026458320</v>
       </c>
       <c r="P11" t="n">
-        <v>10300</v>
+        <v>13000</v>
       </c>
       <c r="Q11" t="n">
-        <v>952</v>
+        <v>6030</v>
       </c>
       <c r="R11" t="n">
-        <v>-210000</v>
+        <v>-679000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>28000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>레미콘 파업 관련 기대감 및 강한 지지선 언급, 당일 상승 추세.</t>
+          <t>주가 하락 예상 및 공매도 관련 언급. 배당금 지급에도 불구하고 주가 하락 가능성에 대한 우려 제기.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['레미콘', '파업', '지지선']</t>
+          <t>['주가 하락', '공매도', '배당금']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>079650</t>
+          <t>0220W0</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3775</v>
+        <v>3790</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+3.71%</t>
+          <t>+4.12%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>2.74</v>
       </c>
       <c r="E12" t="n">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="F12" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G12" t="n">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="H12" t="n">
         <v>3.19</v>
@@ -1530,7 +1530,7 @@
         <v>0.45</v>
       </c>
       <c r="O12" t="n">
-        <v>269615574874</v>
+        <v>271692994567</v>
       </c>
       <c r="P12" t="n">
         <v>8100</v>
@@ -1539,7 +1539,7 @@
         <v>592</v>
       </c>
       <c r="R12" t="n">
-        <v>-816000</v>
+        <v>-731000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -1575,215 +1575,215 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1859000</v>
+        <v>1980</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+3.68%</t>
+          <t>+3.02%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.03</v>
+        <v>-0.1</v>
       </c>
       <c r="E13" t="n">
-        <v>795</v>
+        <v>115</v>
       </c>
       <c r="F13" t="n">
-        <v>452</v>
+        <v>47</v>
       </c>
       <c r="G13" t="n">
-        <v>1755</v>
+        <v>269</v>
       </c>
       <c r="H13" t="n">
-        <v>50.66</v>
+        <v>0.51</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1793000</v>
+        <v>1922</v>
       </c>
       <c r="K13" t="n">
-        <v>1795000</v>
+        <v>1920</v>
       </c>
       <c r="L13" t="n">
-        <v>1883000</v>
+        <v>2165</v>
       </c>
       <c r="M13" t="n">
-        <v>1795000</v>
+        <v>1862</v>
       </c>
       <c r="N13" t="n">
-        <v>50.63</v>
+        <v>0.61</v>
       </c>
       <c r="O13" t="n">
-        <v>4974924459500</v>
+        <v>16932829192</v>
       </c>
       <c r="P13" t="n">
-        <v>2987000</v>
+        <v>2930</v>
       </c>
       <c r="Q13" t="n">
-        <v>277000</v>
+        <v>910</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>154000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>외국인 및 기관 매수세 유입 속 200만원 돌파 기대감. 단기 차익 매물 소화 후 상승 전망.</t>
+          <t>반도체 클러스터 관련주로 언급. 대주주 매도 공시 및 주가 하락 우려.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['외국인매수', '기관매수', '200만원돌파']</t>
+          <t>['반도체 클러스터', '대주주 매도', '주가 전망']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1991</v>
+        <v>1842000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+3.59%</t>
+          <t>+2.73%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.1</v>
+        <v>0.03</v>
       </c>
       <c r="E14" t="n">
-        <v>112</v>
+        <v>793</v>
       </c>
       <c r="F14" t="n">
-        <v>46</v>
+        <v>439</v>
       </c>
       <c r="G14" t="n">
-        <v>263</v>
+        <v>1680</v>
       </c>
       <c r="H14" t="n">
-        <v>0.51</v>
+        <v>50.66</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1922</v>
+        <v>1793000</v>
       </c>
       <c r="K14" t="n">
-        <v>1920</v>
+        <v>1795000</v>
       </c>
       <c r="L14" t="n">
-        <v>2165</v>
+        <v>1883000</v>
       </c>
       <c r="M14" t="n">
-        <v>1862</v>
+        <v>1795000</v>
       </c>
       <c r="N14" t="n">
-        <v>0.61</v>
+        <v>50.63</v>
       </c>
       <c r="O14" t="n">
-        <v>16656079360</v>
+        <v>5283333654500</v>
       </c>
       <c r="P14" t="n">
-        <v>2930</v>
+        <v>2987000</v>
       </c>
       <c r="Q14" t="n">
-        <v>910</v>
+        <v>277000</v>
       </c>
       <c r="R14" t="n">
-        <v>106000</v>
+        <v>180000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>151000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>반도체 클러스터 관련주로 언급. 대주주 매도 공시 및 주가 하락 우려.</t>
+          <t>외인 매수세 유입 및 프로그램 매수세 확인. 호가창 가벼움과 250 목표 주가 달성 기대감.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['반도체 클러스터', '대주주 매도', '주가 전망']</t>
+          <t>['외인 매수', '프로그램 매수', '목표 주가']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>서산</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30700</v>
+        <v>7880</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+3.19%</t>
+          <t>+2.60%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.08</v>
+        <v>1.4</v>
       </c>
       <c r="E15" t="n">
-        <v>645</v>
+        <v>123</v>
       </c>
       <c r="F15" t="n">
-        <v>237</v>
+        <v>77</v>
       </c>
       <c r="G15" t="n">
-        <v>894</v>
+        <v>340</v>
       </c>
       <c r="H15" t="n">
-        <v>0.31</v>
+        <v>1.81</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>29750</v>
+        <v>7680</v>
       </c>
       <c r="K15" t="n">
-        <v>31600</v>
+        <v>7780</v>
       </c>
       <c r="L15" t="n">
-        <v>34200</v>
+        <v>9000</v>
       </c>
       <c r="M15" t="n">
-        <v>28300</v>
+        <v>7750</v>
       </c>
       <c r="N15" t="n">
-        <v>0.23</v>
+        <v>0.41</v>
       </c>
       <c r="O15" t="n">
-        <v>466747258850</v>
+        <v>114868266545</v>
       </c>
       <c r="P15" t="n">
-        <v>39350</v>
+        <v>10300</v>
       </c>
       <c r="Q15" t="n">
-        <v>8200</v>
+        <v>952</v>
       </c>
       <c r="R15" t="n">
-        <v>-1000</v>
+        <v>-211000</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>혈압계 반지 관련 유럽 진출 뉴스에 따른 기대감. 상장폐지 우려와 함께 2차 파동 시작 전망.</t>
+          <t>강력한 지지선 확인 및 상승 추세 기대. 레미콘 파업 이슈와 연계된 긍정적 주가 움직임 전망.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['혈압계', '유럽진출', '2차파동']</t>
+          <t>['지지선', '상승 추세', '레미콘 파업']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,90 +1844,90 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>079650</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>92000</v>
+        <v>12220</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+2.79%</t>
+          <t>+1.92%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.02</v>
+        <v>-2.16</v>
       </c>
       <c r="E16" t="n">
-        <v>325</v>
+        <v>181</v>
       </c>
       <c r="F16" t="n">
-        <v>212</v>
+        <v>103</v>
       </c>
       <c r="G16" t="n">
-        <v>1636</v>
+        <v>409</v>
       </c>
       <c r="H16" t="n">
-        <v>23.61</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>89500</v>
+        <v>11990</v>
       </c>
       <c r="K16" t="n">
-        <v>92000</v>
+        <v>12440</v>
       </c>
       <c r="L16" t="n">
-        <v>94400</v>
+        <v>12800</v>
       </c>
       <c r="M16" t="n">
-        <v>91300</v>
+        <v>11920</v>
       </c>
       <c r="N16" t="n">
-        <v>23.63</v>
+        <v>2.16</v>
       </c>
       <c r="O16" t="n">
-        <v>283027184000</v>
+        <v>45249632925</v>
       </c>
       <c r="P16" t="n">
-        <v>139200</v>
+        <v>36200</v>
       </c>
       <c r="Q16" t="n">
-        <v>57000</v>
+        <v>8920</v>
       </c>
       <c r="R16" t="n">
-        <v>103000</v>
+        <v>22000</v>
       </c>
       <c r="S16" t="n">
-        <v>66000</v>
+        <v>-6000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 원전주 급등 및 SMR 관련 긍정적 전망. 한-프랑스 정상회담 원자력 협력 기대감 반영. 하반기 주도주 가능성 및 대미 투자 수혜 언급.</t>
+          <t>국제 유가 급등에도 불구하고 주가 변동성 없음. 이란 유조선 공격 관련 지정학적 리스크 및 브렌트유 100달러 돌파 가능성 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '한-프랑스']</t>
+          <t>['국제 유가', '지정학적 리스크', '브렌트유']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,90 +1936,90 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12130</v>
+        <v>91100</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+1.17%</t>
+          <t>+1.79%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-2.16</v>
+        <v>-0.02</v>
       </c>
       <c r="E17" t="n">
-        <v>174</v>
+        <v>333</v>
       </c>
       <c r="F17" t="n">
-        <v>99</v>
+        <v>216</v>
       </c>
       <c r="G17" t="n">
-        <v>382</v>
+        <v>1671</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>23.61</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>11990</v>
+        <v>89500</v>
       </c>
       <c r="K17" t="n">
-        <v>12440</v>
+        <v>92000</v>
       </c>
       <c r="L17" t="n">
-        <v>12800</v>
+        <v>94400</v>
       </c>
       <c r="M17" t="n">
-        <v>11920</v>
+        <v>91100</v>
       </c>
       <c r="N17" t="n">
-        <v>2.16</v>
+        <v>23.63</v>
       </c>
       <c r="O17" t="n">
-        <v>43941251465</v>
+        <v>297112392200</v>
       </c>
       <c r="P17" t="n">
-        <v>36200</v>
+        <v>139200</v>
       </c>
       <c r="Q17" t="n">
-        <v>8920</v>
+        <v>57000</v>
       </c>
       <c r="R17" t="n">
-        <v>27000</v>
+        <v>123000</v>
       </c>
       <c r="S17" t="n">
-        <v>-6000</v>
+        <v>96000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>국제 유가 급등에도 불구하고 주가는 큰 변동이 없는 상황. 지정학적 리스크(후티, 사우디, 이란 유조선 공격 등)와 유가 상승 뉴스가 지속적으로 언급되나, 실제 주가 움직임은 이를 반영하지 못하고 있음. 향후 유가 100달러 돌파 여부가 관건.</t>
+          <t>미국 원전주 급등 및 SMR 관련 긍정적 전망. 한-프랑스 정상회담 원자력 협력 기대감 반영. 하반기 주도주 가능성 및 대미 투자 수혜 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['국제유가', '지정학적 리스크', '주가']</t>
+          <t>['원전', 'SMR', '한-프랑스']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>270250</v>
+        <v>8950</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.06</v>
+        <v>-0.36</v>
       </c>
       <c r="E18" t="n">
-        <v>786</v>
+        <v>119</v>
       </c>
       <c r="F18" t="n">
-        <v>480</v>
+        <v>67</v>
       </c>
       <c r="G18" t="n">
-        <v>1526</v>
+        <v>487</v>
       </c>
       <c r="H18" t="n">
-        <v>46.85</v>
+        <v>27.69</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,91 +2067,91 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>269500</v>
+        <v>8940</v>
       </c>
       <c r="K18" t="n">
-        <v>269500</v>
+        <v>8940</v>
       </c>
       <c r="L18" t="n">
-        <v>275000</v>
+        <v>9070</v>
       </c>
       <c r="M18" t="n">
-        <v>268500</v>
+        <v>8710</v>
       </c>
       <c r="N18" t="n">
-        <v>46.79</v>
+        <v>28.05</v>
       </c>
       <c r="O18" t="n">
-        <v>3219942808500</v>
+        <v>29801862235</v>
       </c>
       <c r="P18" t="n">
-        <v>374500</v>
+        <v>17950</v>
       </c>
       <c r="Q18" t="n">
-        <v>70000</v>
+        <v>8120</v>
       </c>
       <c r="R18" t="n">
-        <v>-1252000</v>
+        <v>-309000</v>
       </c>
       <c r="S18" t="n">
-        <v>720000</v>
+        <v>7000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>SK하이닉스와의 주가 격차 확대에 대한 실망감. 자사주 매입 및 공매도 관련 비판.</t>
+          <t>중국산 제품 경쟁력 및 부정적 전망. 주주 불만 및 기업의 낮은 주가 관리 능력 지적. AI 관련 언급은 있으나 구체적 호재는 부재.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['SK하이닉스', '자사주매입', '공매도']</t>
+          <t>['중국산', '주가관리', 'AI']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>102</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8960</v>
+        <v>267750</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>-0.65%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.36</v>
+        <v>0.06</v>
       </c>
       <c r="E19" t="n">
-        <v>112</v>
+        <v>789</v>
       </c>
       <c r="F19" t="n">
-        <v>66</v>
+        <v>481</v>
       </c>
       <c r="G19" t="n">
-        <v>467</v>
+        <v>1578</v>
       </c>
       <c r="H19" t="n">
-        <v>27.69</v>
+        <v>46.85</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,60 +2159,60 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>8940</v>
+        <v>269500</v>
       </c>
       <c r="K19" t="n">
-        <v>8940</v>
+        <v>269500</v>
       </c>
       <c r="L19" t="n">
-        <v>9070</v>
+        <v>275000</v>
       </c>
       <c r="M19" t="n">
-        <v>8710</v>
+        <v>267500</v>
       </c>
       <c r="N19" t="n">
-        <v>28.05</v>
+        <v>46.79</v>
       </c>
       <c r="O19" t="n">
-        <v>28389680550</v>
+        <v>3476334513750</v>
       </c>
       <c r="P19" t="n">
-        <v>17950</v>
+        <v>374500</v>
       </c>
       <c r="Q19" t="n">
-        <v>8120</v>
+        <v>70000</v>
       </c>
       <c r="R19" t="n">
-        <v>-481000</v>
+        <v>-1876000</v>
       </c>
       <c r="S19" t="n">
-        <v>5000</v>
+        <v>784000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>중국산 제품 경쟁력 및 부정적 전망. 주주 불만 및 기업의 낮은 주가 관리 능력 지적. AI 관련 언급은 있으나 구체적 호재는 부재.</t>
+          <t>하이닉스와의 주가 격차 및 경쟁력 약화에 대한 부정적 평가. 노조 관련 이슈 및 자사주 매입 필요성 언급.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['중국산', '주가관리', 'AI']</t>
+          <t>['주가 격차', '경쟁력', '자사주 매입']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -2223,27 +2223,27 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>33600</v>
+        <v>33550</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.47%</t>
+          <t>-1.61%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0.1</v>
       </c>
       <c r="E20" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F20" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G20" t="n">
-        <v>276</v>
+        <v>291</v>
       </c>
       <c r="H20" t="n">
-        <v>52.58</v>
+        <v>52.57</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>21.01</v>
       </c>
       <c r="O20" t="n">
-        <v>75764847575</v>
+        <v>79019619150</v>
       </c>
       <c r="P20" t="n">
         <v>69500</v>
@@ -2275,23 +2275,23 @@
         <v>30400</v>
       </c>
       <c r="R20" t="n">
-        <v>-69000</v>
+        <v>-80000</v>
       </c>
       <c r="S20" t="n">
-        <v>68000</v>
+        <v>58000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>미국 원전 협력 및 발전 5사 통합 가능성에 대한 기대감. SMP 급락 및 정부 정책 변화에 따른 주가 변동성.</t>
+          <t>미국 원전 협력 및 한전기술 움직임 관련 언급.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['원전협력', '발전5사통합', 'SMP']</t>
+          <t>['원전', 'Smp', '공매도']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,21 +2315,21 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19650</v>
+        <v>19430</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.60%</t>
+          <t>-2.70%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.38</v>
       </c>
       <c r="E21" t="n">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="F21" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G21" t="n">
         <v>737</v>
@@ -2352,13 +2352,13 @@
         <v>21300</v>
       </c>
       <c r="M21" t="n">
-        <v>19630</v>
+        <v>19390</v>
       </c>
       <c r="N21" t="n">
         <v>10.47</v>
       </c>
       <c r="O21" t="n">
-        <v>251895259610</v>
+        <v>265922653500</v>
       </c>
       <c r="P21" t="n">
         <v>40350</v>
@@ -2367,14 +2367,14 @@
         <v>3320</v>
       </c>
       <c r="R21" t="n">
-        <v>-1134000</v>
+        <v>-1107000</v>
       </c>
       <c r="S21" t="n">
-        <v>-151000</v>
+        <v>-209000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>원전 사업 참여 기대감 속 공시 확인 후 주가 하락. 차트상 긍정적 흐름.</t>
+          <t>미국 원전 사업 참여 기대감. 계약 체결 공시 확인 및 차트 분석 기반 긍정적 전망.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['원전', '공시', '차트']</t>
+          <t>['원전 사업', '계약 체결', '차트 분석']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10140</v>
+        <v>10120</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.87%</t>
+          <t>-3.07%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0.32</v>
       </c>
       <c r="E22" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F22" t="n">
         <v>71</v>
       </c>
       <c r="G22" t="n">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="H22" t="n">
         <v>0.9399999999999999</v>
@@ -2450,7 +2450,7 @@
         <v>0.62</v>
       </c>
       <c r="O22" t="n">
-        <v>145026298515</v>
+        <v>145997429785</v>
       </c>
       <c r="P22" t="n">
         <v>15960</v>
@@ -2459,7 +2459,7 @@
         <v>3500</v>
       </c>
       <c r="R22" t="n">
-        <v>-11000</v>
+        <v>-50000</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3740</v>
+        <v>3720</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-3.86%</t>
+          <t>-4.37%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>0.52</v>
       </c>
       <c r="E23" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F23" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G23" t="n">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="H23" t="n">
         <v>2.08</v>
@@ -2542,7 +2542,7 @@
         <v>1.56</v>
       </c>
       <c r="O23" t="n">
-        <v>65194789772</v>
+        <v>66063714110</v>
       </c>
       <c r="P23" t="n">
         <v>4335</v>
@@ -2551,7 +2551,7 @@
         <v>1246</v>
       </c>
       <c r="R23" t="n">
-        <v>-519000</v>
+        <v>-599000</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>

--- a/data/trending_integrated_20260909_14.xlsx
+++ b/data/trending_integrated_20260909_14.xlsx
@@ -578,13 +578,13 @@
         <v>-1.06</v>
       </c>
       <c r="E2" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="F2" t="n">
         <v>132</v>
       </c>
       <c r="G2" t="n">
-        <v>1502</v>
+        <v>1544</v>
       </c>
       <c r="H2" t="n">
         <v>0.77</v>
@@ -610,7 +610,7 @@
         <v>1.83</v>
       </c>
       <c r="O2" t="n">
-        <v>29712696155</v>
+        <v>29716539715</v>
       </c>
       <c r="P2" t="n">
         <v>21500</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>FDA 2A상 승인 및 암세포 사멸 관련 획기적 약물 뉴스.</t>
+          <t>미 FDA 2A상 승인 및 병용요법 관련 후속 연구 결과 공개 기대감. 외인 매수세 유입 및 거래량 증가.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['FDA 2A상', '암세포 사멸', '다락손라십']</t>
+          <t>['FDA 2A상', '병용요법', '암치료제']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>-0.08</v>
       </c>
       <c r="E3" t="n">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F3" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G3" t="n">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="H3" t="n">
         <v>0.36</v>
@@ -702,7 +702,7 @@
         <v>0.44</v>
       </c>
       <c r="O3" t="n">
-        <v>232621844225</v>
+        <v>232859628695</v>
       </c>
       <c r="P3" t="n">
         <v>20850</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 SMR 및 가스터빈 관련주 폭등 수혜 기대. 80% 품절주 및 정부 대미 투자 1호 관련 긍정적 전망.</t>
+          <t>미국 SMR 및 원전 관련 수혜 기대감, 품절주 및 높은 변동성.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['SMR', '가스터빈', '품절주']</t>
+          <t>['SMR', '원전', '품절주']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -762,13 +762,13 @@
         <v>0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F4" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G4" t="n">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="H4" t="n">
         <v>2.46</v>
@@ -794,7 +794,7 @@
         <v>2.45</v>
       </c>
       <c r="O4" t="n">
-        <v>37855311285</v>
+        <v>37915610745</v>
       </c>
       <c r="P4" t="n">
         <v>16200</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13700</v>
+        <v>13730</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+16.00%</t>
+          <t>+16.26%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.22</v>
       </c>
       <c r="E5" t="n">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="F5" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G5" t="n">
-        <v>1426</v>
+        <v>1436</v>
       </c>
       <c r="H5" t="n">
         <v>5.64</v>
@@ -886,7 +886,7 @@
         <v>5.42</v>
       </c>
       <c r="O5" t="n">
-        <v>468995254055</v>
+        <v>473665586735</v>
       </c>
       <c r="P5" t="n">
         <v>30200</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7160</v>
+        <v>7180</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+14.38%</t>
+          <t>+14.70%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F6" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G6" t="n">
-        <v>1184</v>
+        <v>1211</v>
       </c>
       <c r="H6" t="n">
         <v>7.4</v>
@@ -978,7 +978,7 @@
         <v>7.35</v>
       </c>
       <c r="O6" t="n">
-        <v>68989792020</v>
+        <v>69202433730</v>
       </c>
       <c r="P6" t="n">
         <v>21500</v>
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>써니전자</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2430</v>
+        <v>53600</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+12.50%</t>
+          <t>+8.83%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.23</v>
+        <v>0.03</v>
       </c>
       <c r="E7" t="n">
-        <v>111</v>
+        <v>159</v>
       </c>
       <c r="F7" t="n">
-        <v>58</v>
+        <v>121</v>
       </c>
       <c r="G7" t="n">
-        <v>240</v>
+        <v>595</v>
       </c>
       <c r="H7" t="n">
-        <v>5.26</v>
+        <v>14.96</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,143 +1055,143 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>2160</v>
+        <v>49250</v>
       </c>
       <c r="K7" t="n">
-        <v>2200</v>
+        <v>53500</v>
       </c>
       <c r="L7" t="n">
-        <v>2705</v>
+        <v>59000</v>
       </c>
       <c r="M7" t="n">
-        <v>2200</v>
+        <v>51600</v>
       </c>
       <c r="N7" t="n">
-        <v>5.49</v>
+        <v>14.93</v>
       </c>
       <c r="O7" t="n">
-        <v>36615516621</v>
+        <v>162020745400</v>
       </c>
       <c r="P7" t="n">
-        <v>2705</v>
+        <v>108900</v>
       </c>
       <c r="Q7" t="n">
-        <v>1418</v>
+        <v>18230</v>
       </c>
       <c r="R7" t="n">
-        <v>22000</v>
+        <v>-215000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>154000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>경영권 분쟁 및 지분 싸움 가능성, 엔비디아 관련 루머 및 단기 과열 언급.</t>
+          <t>수주 기대감 속 목표가 상향 전망, 일부 부정적 실적 발표에도 기대감 유지.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['지분싸움', '엔비디아', '경영권']</t>
+          <t>['수주', '목표가', '매출성장성']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>004770</t>
+          <t>336260</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>53300</v>
+        <v>14760</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+8.22%</t>
+          <t>+7.74%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.03</v>
+        <v>-0.39</v>
       </c>
       <c r="E8" t="n">
-        <v>155</v>
+        <v>249</v>
       </c>
       <c r="F8" t="n">
-        <v>119</v>
+        <v>153</v>
       </c>
       <c r="G8" t="n">
-        <v>579</v>
+        <v>1396</v>
       </c>
       <c r="H8" t="n">
-        <v>14.96</v>
+        <v>1.55</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>49250</v>
+        <v>13700</v>
       </c>
       <c r="K8" t="n">
-        <v>53500</v>
+        <v>14260</v>
       </c>
       <c r="L8" t="n">
-        <v>59000</v>
+        <v>15860</v>
       </c>
       <c r="M8" t="n">
-        <v>51600</v>
+        <v>14210</v>
       </c>
       <c r="N8" t="n">
-        <v>14.93</v>
+        <v>1.94</v>
       </c>
       <c r="O8" t="n">
-        <v>160999870450</v>
+        <v>424072532190</v>
       </c>
       <c r="P8" t="n">
-        <v>108900</v>
+        <v>31500</v>
       </c>
       <c r="Q8" t="n">
-        <v>18230</v>
+        <v>1252</v>
       </c>
       <c r="R8" t="n">
-        <v>-215000</v>
+        <v>590000</v>
       </c>
       <c r="S8" t="n">
-        <v>154000</v>
+        <v>20000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>수주 확정 및 2분기 영업이익 악화에도 불구하고 향후 매출 성장성 및 목표 주가 상향 전망.</t>
+          <t>단기 박스권 돌파 및 불기둥 형성, 2만 목표 상향 기대감.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['수주 확정', '매출 성장성', '목표 주가']</t>
+          <t>['불기둥', '박스권돌파', '우상향']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>336260</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>써니전자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14730</v>
+        <v>2300</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+7.52%</t>
+          <t>+6.48%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.39</v>
+        <v>-0.23</v>
       </c>
       <c r="E9" t="n">
-        <v>244</v>
+        <v>127</v>
       </c>
       <c r="F9" t="n">
-        <v>150</v>
+        <v>63</v>
       </c>
       <c r="G9" t="n">
-        <v>1368</v>
+        <v>278</v>
       </c>
       <c r="H9" t="n">
-        <v>1.55</v>
+        <v>5.26</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>13700</v>
+        <v>2160</v>
       </c>
       <c r="K9" t="n">
-        <v>14260</v>
+        <v>2200</v>
       </c>
       <c r="L9" t="n">
-        <v>15860</v>
+        <v>2705</v>
       </c>
       <c r="M9" t="n">
-        <v>14210</v>
+        <v>2200</v>
       </c>
       <c r="N9" t="n">
-        <v>1.94</v>
+        <v>5.49</v>
       </c>
       <c r="O9" t="n">
-        <v>422097736005</v>
+        <v>39330742400</v>
       </c>
       <c r="P9" t="n">
-        <v>31500</v>
+        <v>2705</v>
       </c>
       <c r="Q9" t="n">
-        <v>1252</v>
+        <v>1418</v>
       </c>
       <c r="R9" t="n">
-        <v>590000</v>
+        <v>22000</v>
       </c>
       <c r="S9" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>단기 박스권 돌파 및 2만 원 목표, 긍정적 차트 분석.</t>
+          <t>기타법인 매수세 유입 속 지분 싸움 및 단기 과열 기대감.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['박스권 돌파', '차트 분석', '우상향']</t>
+          <t>['PBR', '지분싸움', '기타법인']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>004770</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31550</v>
+        <v>6820</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+6.05%</t>
+          <t>+6.07%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.08</v>
+        <v>0.31</v>
       </c>
       <c r="E10" t="n">
-        <v>655</v>
+        <v>345</v>
       </c>
       <c r="F10" t="n">
-        <v>241</v>
+        <v>155</v>
       </c>
       <c r="G10" t="n">
-        <v>914</v>
+        <v>538</v>
       </c>
       <c r="H10" t="n">
-        <v>0.31</v>
+        <v>16.71</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>29750</v>
+        <v>6430</v>
       </c>
       <c r="K10" t="n">
-        <v>31600</v>
+        <v>6400</v>
       </c>
       <c r="L10" t="n">
-        <v>34200</v>
+        <v>7470</v>
       </c>
       <c r="M10" t="n">
-        <v>28300</v>
+        <v>6250</v>
       </c>
       <c r="N10" t="n">
-        <v>0.23</v>
+        <v>16.4</v>
       </c>
       <c r="O10" t="n">
-        <v>481347456925</v>
+        <v>98818522280</v>
       </c>
       <c r="P10" t="n">
-        <v>39350</v>
+        <v>13000</v>
       </c>
       <c r="Q10" t="n">
-        <v>8200</v>
+        <v>6030</v>
       </c>
       <c r="R10" t="n">
-        <v>-1000</v>
+        <v>-679000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>28000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>혈압 반지에 대한 유럽 진출 뉴스 및 2차 파동 전망.</t>
+          <t>주가 하락 예상 및 공매도 관련 언급. 배당금 지급에도 불구하고 주가 하락 가능성에 대한 우려 제기.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['혈압 반지', '유럽 진출', '2차 파동']</t>
+          <t>['주가 하락', '공매도', '배당금']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>0220W0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6780</v>
+        <v>31000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+5.44%</t>
+          <t>+4.20%</t>
         </is>
       </c>
       <c r="D11" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>673</v>
+      </c>
+      <c r="F11" t="n">
+        <v>248</v>
+      </c>
+      <c r="G11" t="n">
+        <v>952</v>
+      </c>
+      <c r="H11" t="n">
         <v>0.31</v>
       </c>
-      <c r="E11" t="n">
-        <v>344</v>
-      </c>
-      <c r="F11" t="n">
-        <v>156</v>
-      </c>
-      <c r="G11" t="n">
-        <v>538</v>
-      </c>
-      <c r="H11" t="n">
-        <v>16.71</v>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>6430</v>
+        <v>29750</v>
       </c>
       <c r="K11" t="n">
-        <v>6400</v>
+        <v>31600</v>
       </c>
       <c r="L11" t="n">
-        <v>7470</v>
+        <v>34200</v>
       </c>
       <c r="M11" t="n">
-        <v>6250</v>
+        <v>28300</v>
       </c>
       <c r="N11" t="n">
-        <v>16.4</v>
+        <v>0.23</v>
       </c>
       <c r="O11" t="n">
-        <v>98026458320</v>
+        <v>492789306325</v>
       </c>
       <c r="P11" t="n">
-        <v>13000</v>
+        <v>39350</v>
       </c>
       <c r="Q11" t="n">
-        <v>6030</v>
+        <v>8200</v>
       </c>
       <c r="R11" t="n">
-        <v>-679000</v>
+        <v>-1000</v>
       </c>
       <c r="S11" t="n">
-        <v>28000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>주가 하락 예상 및 공매도 관련 언급. 배당금 지급에도 불구하고 주가 하락 가능성에 대한 우려 제기.</t>
+          <t>혈압 반지 관련 유럽 진출 뉴스 및 2차 파동 시작 기대감.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['주가 하락', '공매도', '배당금']</t>
+          <t>['혈압반지', '유럽진출', '2차파동']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0220W0</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3790</v>
+        <v>3780</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+4.12%</t>
+          <t>+3.85%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>2.74</v>
       </c>
       <c r="E12" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F12" t="n">
         <v>124</v>
       </c>
       <c r="G12" t="n">
-        <v>493</v>
+        <v>507</v>
       </c>
       <c r="H12" t="n">
         <v>3.19</v>
@@ -1530,7 +1530,7 @@
         <v>0.45</v>
       </c>
       <c r="O12" t="n">
-        <v>271692994567</v>
+        <v>272260110861</v>
       </c>
       <c r="P12" t="n">
         <v>8100</v>
@@ -1575,267 +1575,267 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1980</v>
+        <v>1849000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+3.02%</t>
+          <t>+3.12%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.1</v>
+        <v>0.03</v>
       </c>
       <c r="E13" t="n">
-        <v>115</v>
+        <v>791</v>
       </c>
       <c r="F13" t="n">
-        <v>47</v>
+        <v>433</v>
       </c>
       <c r="G13" t="n">
-        <v>269</v>
+        <v>1692</v>
       </c>
       <c r="H13" t="n">
-        <v>0.51</v>
+        <v>50.66</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1922</v>
+        <v>1793000</v>
       </c>
       <c r="K13" t="n">
-        <v>1920</v>
+        <v>1795000</v>
       </c>
       <c r="L13" t="n">
-        <v>2165</v>
+        <v>1883000</v>
       </c>
       <c r="M13" t="n">
-        <v>1862</v>
+        <v>1795000</v>
       </c>
       <c r="N13" t="n">
-        <v>0.61</v>
+        <v>50.63</v>
       </c>
       <c r="O13" t="n">
-        <v>16932829192</v>
+        <v>5441594671000</v>
       </c>
       <c r="P13" t="n">
-        <v>2930</v>
+        <v>2987000</v>
       </c>
       <c r="Q13" t="n">
-        <v>910</v>
+        <v>277000</v>
       </c>
       <c r="R13" t="n">
-        <v>154000</v>
+        <v>180000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>151000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>반도체 클러스터 관련주로 언급. 대주주 매도 공시 및 주가 하락 우려.</t>
+          <t>외인 매수세 지속 및 상승 추세 전환 신호 포착, 190 돌파 기대감.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['반도체 클러스터', '대주주 매도', '주가 전망']</t>
+          <t>['외인매수', '상승추세', '자사주매입']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1842000</v>
+        <v>1974</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+2.73%</t>
+          <t>+2.71%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.03</v>
+        <v>-0.1</v>
       </c>
       <c r="E14" t="n">
-        <v>793</v>
+        <v>118</v>
       </c>
       <c r="F14" t="n">
-        <v>439</v>
+        <v>47</v>
       </c>
       <c r="G14" t="n">
-        <v>1680</v>
+        <v>275</v>
       </c>
       <c r="H14" t="n">
-        <v>50.66</v>
+        <v>0.51</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1793000</v>
+        <v>1922</v>
       </c>
       <c r="K14" t="n">
-        <v>1795000</v>
+        <v>1920</v>
       </c>
       <c r="L14" t="n">
-        <v>1883000</v>
+        <v>2165</v>
       </c>
       <c r="M14" t="n">
-        <v>1795000</v>
+        <v>1862</v>
       </c>
       <c r="N14" t="n">
-        <v>50.63</v>
+        <v>0.61</v>
       </c>
       <c r="O14" t="n">
-        <v>5283333654500</v>
+        <v>17055578141</v>
       </c>
       <c r="P14" t="n">
-        <v>2987000</v>
+        <v>2930</v>
       </c>
       <c r="Q14" t="n">
-        <v>277000</v>
+        <v>910</v>
       </c>
       <c r="R14" t="n">
-        <v>180000</v>
+        <v>154000</v>
       </c>
       <c r="S14" t="n">
-        <v>151000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>외인 매수세 유입 및 프로그램 매수세 확인. 호가창 가벼움과 250 목표 주가 달성 기대감.</t>
+          <t>반도체 클러스터 관련주로 언급. 대주주 매도 공시 및 주가 하락 우려.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['외인 매수', '프로그램 매수', '목표 주가']</t>
+          <t>['반도체 클러스터', '대주주 매도', '주가 전망']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>서산</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7880</v>
+        <v>91300</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+2.60%</t>
+          <t>+2.01%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.4</v>
+        <v>-0.02</v>
       </c>
       <c r="E15" t="n">
-        <v>123</v>
+        <v>343</v>
       </c>
       <c r="F15" t="n">
-        <v>77</v>
+        <v>221</v>
       </c>
       <c r="G15" t="n">
-        <v>340</v>
+        <v>1690</v>
       </c>
       <c r="H15" t="n">
-        <v>1.81</v>
+        <v>23.61</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>7680</v>
+        <v>89500</v>
       </c>
       <c r="K15" t="n">
-        <v>7780</v>
+        <v>92000</v>
       </c>
       <c r="L15" t="n">
-        <v>9000</v>
+        <v>94400</v>
       </c>
       <c r="M15" t="n">
-        <v>7750</v>
+        <v>91100</v>
       </c>
       <c r="N15" t="n">
-        <v>0.41</v>
+        <v>23.63</v>
       </c>
       <c r="O15" t="n">
-        <v>114868266545</v>
+        <v>305586070500</v>
       </c>
       <c r="P15" t="n">
-        <v>10300</v>
+        <v>139200</v>
       </c>
       <c r="Q15" t="n">
-        <v>952</v>
+        <v>57000</v>
       </c>
       <c r="R15" t="n">
-        <v>-211000</v>
+        <v>123000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>96000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>강력한 지지선 확인 및 상승 추세 기대. 레미콘 파업 이슈와 연계된 긍정적 주가 움직임 전망.</t>
+          <t>미국 원전주 급등 및 SMR 관련 긍정적 전망. 한-프랑스 정상회담 원자력 협력 기대감 반영. 하반기 주도주 가능성 및 대미 투자 수혜 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['지지선', '상승 추세', '레미콘 파업']</t>
+          <t>['원전', 'SMR', '한-프랑스']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,90 +1844,90 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>079650</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>서산</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12220</v>
+        <v>7830</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+1.92%</t>
+          <t>+1.95%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-2.16</v>
+        <v>1.4</v>
       </c>
       <c r="E16" t="n">
-        <v>181</v>
+        <v>128</v>
       </c>
       <c r="F16" t="n">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="G16" t="n">
-        <v>409</v>
+        <v>353</v>
       </c>
       <c r="H16" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>7680</v>
+      </c>
+      <c r="K16" t="n">
+        <v>7780</v>
+      </c>
+      <c r="L16" t="n">
+        <v>9000</v>
+      </c>
+      <c r="M16" t="n">
+        <v>7750</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="O16" t="n">
+        <v>116026744840</v>
+      </c>
+      <c r="P16" t="n">
+        <v>10300</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>952</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-211000</v>
+      </c>
+      <c r="S16" t="n">
         <v>0</v>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>MarketType.KOSDAQ</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>11990</v>
-      </c>
-      <c r="K16" t="n">
-        <v>12440</v>
-      </c>
-      <c r="L16" t="n">
-        <v>12800</v>
-      </c>
-      <c r="M16" t="n">
-        <v>11920</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="O16" t="n">
-        <v>45249632925</v>
-      </c>
-      <c r="P16" t="n">
-        <v>36200</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>8920</v>
-      </c>
-      <c r="R16" t="n">
-        <v>22000</v>
-      </c>
-      <c r="S16" t="n">
-        <v>-6000</v>
-      </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>국제 유가 급등에도 불구하고 주가 변동성 없음. 이란 유조선 공격 관련 지정학적 리스크 및 브렌트유 100달러 돌파 가능성 언급.</t>
+          <t>레미콘 파업 및 강한 지지선 구간, 상한가 기대감.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['국제 유가', '지정학적 리스크', '브렌트유']</t>
+          <t>['레미콘', '지지선', '상한가']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,90 +1936,90 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>079650</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>91100</v>
+        <v>12140</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+1.79%</t>
+          <t>+1.25%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.02</v>
+        <v>-2.16</v>
       </c>
       <c r="E17" t="n">
-        <v>333</v>
+        <v>182</v>
       </c>
       <c r="F17" t="n">
-        <v>216</v>
+        <v>103</v>
       </c>
       <c r="G17" t="n">
-        <v>1671</v>
+        <v>410</v>
       </c>
       <c r="H17" t="n">
-        <v>23.61</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>89500</v>
+        <v>11990</v>
       </c>
       <c r="K17" t="n">
-        <v>92000</v>
+        <v>12440</v>
       </c>
       <c r="L17" t="n">
-        <v>94400</v>
+        <v>12800</v>
       </c>
       <c r="M17" t="n">
-        <v>91100</v>
+        <v>11920</v>
       </c>
       <c r="N17" t="n">
-        <v>23.63</v>
+        <v>2.16</v>
       </c>
       <c r="O17" t="n">
-        <v>297112392200</v>
+        <v>45702533465</v>
       </c>
       <c r="P17" t="n">
-        <v>139200</v>
+        <v>36200</v>
       </c>
       <c r="Q17" t="n">
-        <v>57000</v>
+        <v>8920</v>
       </c>
       <c r="R17" t="n">
-        <v>123000</v>
+        <v>22000</v>
       </c>
       <c r="S17" t="n">
-        <v>96000</v>
+        <v>-6000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 원전주 급등 및 SMR 관련 긍정적 전망. 한-프랑스 정상회담 원자력 협력 기대감 반영. 하반기 주도주 가능성 및 대미 투자 수혜 언급.</t>
+          <t>국제 유가 급등에도 불구하고 주가 변동성 없음. 이란 유조선 공격 관련 지정학적 리스크 및 브렌트유 100달러 돌파 가능성 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '한-프랑스']</t>
+          <t>['국제 유가', '지정학적 리스크', '브렌트유']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8950</v>
+        <v>8960</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.22%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.36</v>
       </c>
       <c r="E18" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F18" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G18" t="n">
-        <v>487</v>
+        <v>498</v>
       </c>
       <c r="H18" t="n">
         <v>27.69</v>
@@ -2082,7 +2082,7 @@
         <v>28.05</v>
       </c>
       <c r="O18" t="n">
-        <v>29801862235</v>
+        <v>31181080545</v>
       </c>
       <c r="P18" t="n">
         <v>17950</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>중국산 제품 경쟁력 및 부정적 전망. 주주 불만 및 기업의 낮은 주가 관리 능력 지적. AI 관련 언급은 있으나 구체적 호재는 부재.</t>
+          <t>AI 관련 기대감 있으나, 개인 투자자 매수 집중 및 기업 성장성 의문 제기.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['중국산', '주가관리', 'AI']</t>
+          <t>['AI', '개인투자자', '성장성']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>267750</v>
+        <v>268750</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.65%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.06</v>
       </c>
       <c r="E19" t="n">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="F19" t="n">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="G19" t="n">
-        <v>1578</v>
+        <v>1682</v>
       </c>
       <c r="H19" t="n">
         <v>46.85</v>
@@ -2174,7 +2174,7 @@
         <v>46.79</v>
       </c>
       <c r="O19" t="n">
-        <v>3476334513750</v>
+        <v>3611520617000</v>
       </c>
       <c r="P19" t="n">
         <v>374500</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>하이닉스와의 주가 격차 및 경쟁력 약화에 대한 부정적 평가. 노조 관련 이슈 및 자사주 매입 필요성 언급.</t>
+          <t>노조 이슈 및 하이닉스와의 주가 비교 속 부정적 전망.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['주가 격차', '경쟁력', '자사주 매입']</t>
+          <t>['노조', '하이닉스', '주가']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>33550</v>
+        <v>33600</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.61%</t>
+          <t>-1.47%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0.1</v>
       </c>
       <c r="E20" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F20" t="n">
         <v>64</v>
       </c>
       <c r="G20" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="H20" t="n">
         <v>52.57</v>
@@ -2266,7 +2266,7 @@
         <v>21.01</v>
       </c>
       <c r="O20" t="n">
-        <v>79019619150</v>
+        <v>80963310875</v>
       </c>
       <c r="P20" t="n">
         <v>69500</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19430</v>
+        <v>19410</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.70%</t>
+          <t>-2.80%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.38</v>
       </c>
       <c r="E21" t="n">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="F21" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G21" t="n">
-        <v>737</v>
+        <v>743</v>
       </c>
       <c r="H21" t="n">
         <v>10.85</v>
@@ -2352,13 +2352,13 @@
         <v>21300</v>
       </c>
       <c r="M21" t="n">
-        <v>19390</v>
+        <v>19350</v>
       </c>
       <c r="N21" t="n">
         <v>10.47</v>
       </c>
       <c r="O21" t="n">
-        <v>265922653500</v>
+        <v>271933828105</v>
       </c>
       <c r="P21" t="n">
         <v>40350</v>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>미국 원전 사업 참여 기대감. 계약 체결 공시 확인 및 차트 분석 기반 긍정적 전망.</t>
+          <t>원전 관련 호재 속 계약 체결 공시 확인, 일부 투자자 기대감.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['원전 사업', '계약 체결', '차트 분석']</t>
+          <t>['원전', '공시', '계약체결']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10120</v>
+        <v>10090</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-3.07%</t>
+          <t>-3.35%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0.32</v>
       </c>
       <c r="E22" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F22" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G22" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="H22" t="n">
         <v>0.9399999999999999</v>
@@ -2450,7 +2450,7 @@
         <v>0.62</v>
       </c>
       <c r="O22" t="n">
-        <v>145997429785</v>
+        <v>146494818395</v>
       </c>
       <c r="P22" t="n">
         <v>15960</v>
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3720</v>
+        <v>3740</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-4.37%</t>
+          <t>-3.86%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>0.52</v>
       </c>
       <c r="E23" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F23" t="n">
         <v>52</v>
       </c>
       <c r="G23" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H23" t="n">
         <v>2.08</v>
@@ -2542,7 +2542,7 @@
         <v>1.56</v>
       </c>
       <c r="O23" t="n">
-        <v>66063714110</v>
+        <v>66503090377</v>
       </c>
       <c r="P23" t="n">
         <v>4335</v>

--- a/data/trending_integrated_20260909_14.xlsx
+++ b/data/trending_integrated_20260909_14.xlsx
@@ -578,13 +578,13 @@
         <v>-1.06</v>
       </c>
       <c r="E2" t="n">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F2" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G2" t="n">
-        <v>1544</v>
+        <v>1564</v>
       </c>
       <c r="H2" t="n">
         <v>0.77</v>
@@ -610,7 +610,7 @@
         <v>1.83</v>
       </c>
       <c r="O2" t="n">
-        <v>29716539715</v>
+        <v>29737412175</v>
       </c>
       <c r="P2" t="n">
         <v>21500</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미 FDA 2A상 승인 및 병용요법 관련 후속 연구 결과 공개 기대감. 외인 매수세 유입 및 거래량 증가.</t>
+          <t>미 FDA 2A상 승인 및 다락손라십 대비 우수한 효능 확인. 5연상 기대감 고조.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['FDA 2A상', '병용요법', '암치료제']</t>
+          <t>['FDA', '암치료제', '효능']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>-0.08</v>
       </c>
       <c r="E3" t="n">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F3" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G3" t="n">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="H3" t="n">
         <v>0.36</v>
@@ -702,7 +702,7 @@
         <v>0.44</v>
       </c>
       <c r="O3" t="n">
-        <v>232859628695</v>
+        <v>233014216615</v>
       </c>
       <c r="P3" t="n">
         <v>20850</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 SMR 및 원전 관련 수혜 기대감, 품절주 및 높은 변동성.</t>
+          <t>미국 증시 SMR 관련주 동반 급등 및 품절주 특징 부각. 신규 재료 기대감.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['SMR', '원전', '품절주']</t>
+          <t>['SMR', '품절주', '재료']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -762,13 +762,13 @@
         <v>0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F4" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G4" t="n">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="H4" t="n">
         <v>2.46</v>
@@ -794,7 +794,7 @@
         <v>2.45</v>
       </c>
       <c r="O4" t="n">
-        <v>37915610745</v>
+        <v>37934650605</v>
       </c>
       <c r="P4" t="n">
         <v>16200</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13730</v>
+        <v>13930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+16.26%</t>
+          <t>+17.95%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.22</v>
       </c>
       <c r="E5" t="n">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="F5" t="n">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="G5" t="n">
-        <v>1436</v>
+        <v>1442</v>
       </c>
       <c r="H5" t="n">
         <v>5.64</v>
@@ -886,7 +886,7 @@
         <v>5.42</v>
       </c>
       <c r="O5" t="n">
-        <v>473665586735</v>
+        <v>477472931945</v>
       </c>
       <c r="P5" t="n">
         <v>30200</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7180</v>
+        <v>7190</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+14.70%</t>
+          <t>+14.86%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F6" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="G6" t="n">
-        <v>1211</v>
+        <v>1260</v>
       </c>
       <c r="H6" t="n">
         <v>7.4</v>
@@ -978,7 +978,7 @@
         <v>7.35</v>
       </c>
       <c r="O6" t="n">
-        <v>69202433730</v>
+        <v>69494672970</v>
       </c>
       <c r="P6" t="n">
         <v>21500</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>뎅기열 중간 발표 및 오가노이드 실험 결과에 대한 기대감. 다락손라십 췌장암 치료제 및 페니트리움 항암 치료제 개발 진행.</t>
+          <t>뎅기열 치료제 및 췌장암 치료제 관련 데이터 발표 기대. 공매도와의 경쟁 심화.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['뎅기열', '오가노이드', '항암 치료제']</t>
+          <t>['뎅기열', '췌장암', '공매도']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>53600</v>
+        <v>53800</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+8.83%</t>
+          <t>+9.24%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.03</v>
       </c>
       <c r="E7" t="n">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="F7" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G7" t="n">
-        <v>595</v>
+        <v>609</v>
       </c>
       <c r="H7" t="n">
         <v>14.96</v>
@@ -1070,7 +1070,7 @@
         <v>14.93</v>
       </c>
       <c r="O7" t="n">
-        <v>162020745400</v>
+        <v>163034458000</v>
       </c>
       <c r="P7" t="n">
         <v>108900</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>수주 기대감 속 목표가 상향 전망, 일부 부정적 실적 발표에도 기대감 유지.</t>
+          <t>대규모 수주 및 2분기 영업이익 흑자 전환 기대감. 목표가 상향 논의 활발.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['수주', '목표가', '매출성장성']</t>
+          <t>['수주', '영업이익', '목표가']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14760</v>
+        <v>14870</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+7.74%</t>
+          <t>+8.54%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.39</v>
       </c>
       <c r="E8" t="n">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="F8" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="G8" t="n">
-        <v>1396</v>
+        <v>1423</v>
       </c>
       <c r="H8" t="n">
         <v>1.55</v>
@@ -1162,7 +1162,7 @@
         <v>1.94</v>
       </c>
       <c r="O8" t="n">
-        <v>424072532190</v>
+        <v>427323960390</v>
       </c>
       <c r="P8" t="n">
         <v>31500</v>
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>써니전자</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2300</v>
+        <v>6820</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+6.48%</t>
+          <t>+6.07%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.23</v>
+        <v>0.31</v>
       </c>
       <c r="E9" t="n">
-        <v>127</v>
+        <v>347</v>
       </c>
       <c r="F9" t="n">
-        <v>63</v>
+        <v>155</v>
       </c>
       <c r="G9" t="n">
-        <v>278</v>
+        <v>545</v>
       </c>
       <c r="H9" t="n">
-        <v>5.26</v>
+        <v>16.71</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>2160</v>
+        <v>6430</v>
       </c>
       <c r="K9" t="n">
-        <v>2200</v>
+        <v>6400</v>
       </c>
       <c r="L9" t="n">
-        <v>2705</v>
+        <v>7470</v>
       </c>
       <c r="M9" t="n">
-        <v>2200</v>
+        <v>6250</v>
       </c>
       <c r="N9" t="n">
-        <v>5.49</v>
+        <v>16.4</v>
       </c>
       <c r="O9" t="n">
-        <v>39330742400</v>
+        <v>99305201865</v>
       </c>
       <c r="P9" t="n">
-        <v>2705</v>
+        <v>13000</v>
       </c>
       <c r="Q9" t="n">
-        <v>1418</v>
+        <v>6030</v>
       </c>
       <c r="R9" t="n">
-        <v>22000</v>
+        <v>-679000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>28000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>기타법인 매수세 유입 속 지분 싸움 및 단기 과열 기대감.</t>
+          <t>주가 하락 예상 및 공매도 관련 언급. 배당금 지급에도 불구하고 주가 하락 가능성에 대한 우려 제기.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['PBR', '지분싸움', '기타법인']</t>
+          <t>['주가 하락', '공매도', '배당금']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>004770</t>
+          <t>0220W0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6820</v>
+        <v>31250</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+6.07%</t>
+          <t>+5.04%</t>
         </is>
       </c>
       <c r="D10" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>694</v>
+      </c>
+      <c r="F10" t="n">
+        <v>251</v>
+      </c>
+      <c r="G10" t="n">
+        <v>993</v>
+      </c>
+      <c r="H10" t="n">
         <v>0.31</v>
       </c>
-      <c r="E10" t="n">
-        <v>345</v>
-      </c>
-      <c r="F10" t="n">
-        <v>155</v>
-      </c>
-      <c r="G10" t="n">
-        <v>538</v>
-      </c>
-      <c r="H10" t="n">
-        <v>16.71</v>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>6430</v>
+        <v>29750</v>
       </c>
       <c r="K10" t="n">
-        <v>6400</v>
+        <v>31600</v>
       </c>
       <c r="L10" t="n">
-        <v>7470</v>
+        <v>34200</v>
       </c>
       <c r="M10" t="n">
-        <v>6250</v>
+        <v>28300</v>
       </c>
       <c r="N10" t="n">
-        <v>16.4</v>
+        <v>0.23</v>
       </c>
       <c r="O10" t="n">
-        <v>98818522280</v>
+        <v>508127145875</v>
       </c>
       <c r="P10" t="n">
-        <v>13000</v>
+        <v>39350</v>
       </c>
       <c r="Q10" t="n">
-        <v>6030</v>
+        <v>8200</v>
       </c>
       <c r="R10" t="n">
-        <v>-679000</v>
+        <v>-1000</v>
       </c>
       <c r="S10" t="n">
-        <v>28000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>주가 하락 예상 및 공매도 관련 언급. 배당금 지급에도 불구하고 주가 하락 가능성에 대한 우려 제기.</t>
+          <t>세계 최초 혈압 반지의 유럽 진출 뉴스 확인. 최저점 매수 논의 및 2차 파동 기대.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['주가 하락', '공매도', '배당금']</t>
+          <t>['혈압반지', '유럽진출', '최저점']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0220W0</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>써니전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>31000</v>
+        <v>2245</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+4.20%</t>
+          <t>+3.94%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.08</v>
+        <v>-0.23</v>
       </c>
       <c r="E11" t="n">
-        <v>673</v>
+        <v>147</v>
       </c>
       <c r="F11" t="n">
-        <v>248</v>
+        <v>72</v>
       </c>
       <c r="G11" t="n">
-        <v>952</v>
+        <v>314</v>
       </c>
       <c r="H11" t="n">
-        <v>0.31</v>
+        <v>5.26</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>29750</v>
+        <v>2160</v>
       </c>
       <c r="K11" t="n">
-        <v>31600</v>
+        <v>2200</v>
       </c>
       <c r="L11" t="n">
-        <v>34200</v>
+        <v>2705</v>
       </c>
       <c r="M11" t="n">
-        <v>28300</v>
+        <v>2200</v>
       </c>
       <c r="N11" t="n">
-        <v>0.23</v>
+        <v>5.49</v>
       </c>
       <c r="O11" t="n">
-        <v>492789306325</v>
+        <v>41787657462</v>
       </c>
       <c r="P11" t="n">
-        <v>39350</v>
+        <v>2705</v>
       </c>
       <c r="Q11" t="n">
-        <v>8200</v>
+        <v>1418</v>
       </c>
       <c r="R11" t="n">
-        <v>-1000</v>
+        <v>22000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>혈압 반지 관련 유럽 진출 뉴스 및 2차 파동 시작 기대감.</t>
+          <t>기타 법인 장내 매수세 유입 및 지분 싸움 기대감. 단기 과열 우려도 존재.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['혈압반지', '유럽진출', '2차파동']</t>
+          <t>['PBR', '지분싸움', '기타법인']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>004770</t>
         </is>
       </c>
     </row>
@@ -1498,13 +1498,13 @@
         <v>2.74</v>
       </c>
       <c r="E12" t="n">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="F12" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G12" t="n">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="H12" t="n">
         <v>3.19</v>
@@ -1530,7 +1530,7 @@
         <v>0.45</v>
       </c>
       <c r="O12" t="n">
-        <v>272260110861</v>
+        <v>273083000735</v>
       </c>
       <c r="P12" t="n">
         <v>8100</v>
@@ -1575,184 +1575,184 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1849000</v>
+        <v>1986</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+3.12%</t>
+          <t>+3.33%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.03</v>
+        <v>-0.1</v>
       </c>
       <c r="E13" t="n">
-        <v>791</v>
+        <v>118</v>
       </c>
       <c r="F13" t="n">
-        <v>433</v>
+        <v>47</v>
       </c>
       <c r="G13" t="n">
-        <v>1692</v>
+        <v>277</v>
       </c>
       <c r="H13" t="n">
-        <v>50.66</v>
+        <v>0.51</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1793000</v>
+        <v>1922</v>
       </c>
       <c r="K13" t="n">
-        <v>1795000</v>
+        <v>1920</v>
       </c>
       <c r="L13" t="n">
-        <v>1883000</v>
+        <v>2165</v>
       </c>
       <c r="M13" t="n">
-        <v>1795000</v>
+        <v>1862</v>
       </c>
       <c r="N13" t="n">
-        <v>50.63</v>
+        <v>0.61</v>
       </c>
       <c r="O13" t="n">
-        <v>5441594671000</v>
+        <v>17132888371</v>
       </c>
       <c r="P13" t="n">
-        <v>2987000</v>
+        <v>2930</v>
       </c>
       <c r="Q13" t="n">
-        <v>277000</v>
+        <v>910</v>
       </c>
       <c r="R13" t="n">
-        <v>180000</v>
+        <v>154000</v>
       </c>
       <c r="S13" t="n">
-        <v>151000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>외인 매수세 지속 및 상승 추세 전환 신호 포착, 190 돌파 기대감.</t>
+          <t>반도체 클러스터 관련주로 언급. 대주주 매도 공시 및 주가 하락 우려.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['외인매수', '상승추세', '자사주매입']</t>
+          <t>['반도체 클러스터', '대주주 매도', '주가 전망']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1974</v>
+        <v>1851000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+2.71%</t>
+          <t>+3.23%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.1</v>
+        <v>0.03</v>
       </c>
       <c r="E14" t="n">
-        <v>118</v>
+        <v>792</v>
       </c>
       <c r="F14" t="n">
-        <v>47</v>
+        <v>438</v>
       </c>
       <c r="G14" t="n">
-        <v>275</v>
+        <v>1711</v>
       </c>
       <c r="H14" t="n">
-        <v>0.51</v>
+        <v>50.66</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1922</v>
+        <v>1793000</v>
       </c>
       <c r="K14" t="n">
-        <v>1920</v>
+        <v>1795000</v>
       </c>
       <c r="L14" t="n">
-        <v>2165</v>
+        <v>1883000</v>
       </c>
       <c r="M14" t="n">
-        <v>1862</v>
+        <v>1795000</v>
       </c>
       <c r="N14" t="n">
-        <v>0.61</v>
+        <v>50.63</v>
       </c>
       <c r="O14" t="n">
-        <v>17055578141</v>
+        <v>5555893967500</v>
       </c>
       <c r="P14" t="n">
-        <v>2930</v>
+        <v>2987000</v>
       </c>
       <c r="Q14" t="n">
-        <v>910</v>
+        <v>277000</v>
       </c>
       <c r="R14" t="n">
-        <v>154000</v>
+        <v>180000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>151000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>반도체 클러스터 관련주로 언급. 대주주 매도 공시 및 주가 하락 우려.</t>
+          <t>외국인 및 기관의 지속적인 매수세 유입 확인. 상승 추세 전환 신호 및 악성 매물 소화 기대.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['반도체 클러스터', '대주주 매도', '주가 전망']</t>
+          <t>['외인매수', '상승추세', '악성매물']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>91300</v>
+        <v>91600</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+2.01%</t>
+          <t>+2.35%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.02</v>
       </c>
       <c r="E15" t="n">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="F15" t="n">
         <v>221</v>
       </c>
       <c r="G15" t="n">
-        <v>1690</v>
+        <v>1711</v>
       </c>
       <c r="H15" t="n">
         <v>23.61</v>
@@ -1806,7 +1806,7 @@
         <v>23.63</v>
       </c>
       <c r="O15" t="n">
-        <v>305586070500</v>
+        <v>309774192850</v>
       </c>
       <c r="P15" t="n">
         <v>139200</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7830</v>
+        <v>7730</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+1.95%</t>
+          <t>+0.65%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>1.4</v>
       </c>
       <c r="E16" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="F16" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G16" t="n">
-        <v>353</v>
+        <v>378</v>
       </c>
       <c r="H16" t="n">
         <v>1.81</v>
@@ -1892,13 +1892,13 @@
         <v>9000</v>
       </c>
       <c r="M16" t="n">
-        <v>7750</v>
+        <v>7690</v>
       </c>
       <c r="N16" t="n">
         <v>0.41</v>
       </c>
       <c r="O16" t="n">
-        <v>116026744840</v>
+        <v>117384898455</v>
       </c>
       <c r="P16" t="n">
         <v>10300</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>레미콘 파업 및 강한 지지선 구간, 상한가 기대감.</t>
+          <t>레미콘 파업 시작 및 대장주로서의 강세 기대. 하지만 전반적인 상승 동력은 약함.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['레미콘', '지지선', '상한가']</t>
+          <t>['레미콘', '대장주', '파업']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12140</v>
+        <v>12050</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+1.25%</t>
+          <t>+0.50%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-2.16</v>
       </c>
       <c r="E17" t="n">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="F17" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G17" t="n">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1990,7 +1990,7 @@
         <v>2.16</v>
       </c>
       <c r="O17" t="n">
-        <v>45702533465</v>
+        <v>46532096305</v>
       </c>
       <c r="P17" t="n">
         <v>36200</v>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8960</v>
+        <v>8945</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.36</v>
       </c>
       <c r="E18" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F18" t="n">
         <v>68</v>
       </c>
       <c r="G18" t="n">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="H18" t="n">
         <v>27.69</v>
@@ -2082,7 +2082,7 @@
         <v>28.05</v>
       </c>
       <c r="O18" t="n">
-        <v>31181080545</v>
+        <v>31730490160</v>
       </c>
       <c r="P18" t="n">
         <v>17950</v>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -2142,13 +2142,13 @@
         <v>0.06</v>
       </c>
       <c r="E19" t="n">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="F19" t="n">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="G19" t="n">
-        <v>1682</v>
+        <v>1770</v>
       </c>
       <c r="H19" t="n">
         <v>46.85</v>
@@ -2174,7 +2174,7 @@
         <v>46.79</v>
       </c>
       <c r="O19" t="n">
-        <v>3611520617000</v>
+        <v>3672169233250</v>
       </c>
       <c r="P19" t="n">
         <v>374500</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>노조 이슈 및 하이닉스와의 주가 비교 속 부정적 전망.</t>
+          <t>하이닉스와의 주가 비교 열세 및 경영진에 대한 부정적 의견 대두.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['노조', '하이닉스', '주가']</t>
+          <t>['하이닉스', '주가', '경영진']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>33600</v>
+        <v>33625</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.47%</t>
+          <t>-1.39%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0.1</v>
       </c>
       <c r="E20" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F20" t="n">
         <v>64</v>
       </c>
       <c r="G20" t="n">
-        <v>293</v>
+        <v>318</v>
       </c>
       <c r="H20" t="n">
         <v>52.57</v>
@@ -2266,7 +2266,7 @@
         <v>21.01</v>
       </c>
       <c r="O20" t="n">
-        <v>80963310875</v>
+        <v>82740620325</v>
       </c>
       <c r="P20" t="n">
         <v>69500</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>미국 원전 협력 및 한전기술 움직임 관련 언급.</t>
+          <t>한국-프랑스 차세대 원전 협력 뉴스 및 25조 선납매 논의. 공매도 세력의 움직임 주시.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['원전', 'Smp', '공매도']</t>
+          <t>['원전', '선납매', '공매도']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19410</v>
+        <v>19420</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.80%</t>
+          <t>-2.75%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.38</v>
       </c>
       <c r="E21" t="n">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="F21" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G21" t="n">
-        <v>743</v>
+        <v>753</v>
       </c>
       <c r="H21" t="n">
         <v>10.85</v>
@@ -2358,7 +2358,7 @@
         <v>10.47</v>
       </c>
       <c r="O21" t="n">
-        <v>271933828105</v>
+        <v>276765273045</v>
       </c>
       <c r="P21" t="n">
         <v>40350</v>
@@ -2403,70 +2403,70 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10090</v>
+        <v>3750</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-3.35%</t>
+          <t>-3.60%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.32</v>
+        <v>0.52</v>
       </c>
       <c r="E22" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F22" t="n">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="G22" t="n">
-        <v>229</v>
+        <v>196</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.08</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>10440</v>
+        <v>3890</v>
       </c>
       <c r="K22" t="n">
-        <v>10180</v>
+        <v>3890</v>
       </c>
       <c r="L22" t="n">
-        <v>11340</v>
+        <v>4115</v>
       </c>
       <c r="M22" t="n">
-        <v>9980</v>
+        <v>3700</v>
       </c>
       <c r="N22" t="n">
-        <v>0.62</v>
+        <v>1.56</v>
       </c>
       <c r="O22" t="n">
-        <v>146494818395</v>
+        <v>66740430704</v>
       </c>
       <c r="P22" t="n">
-        <v>15960</v>
+        <v>4335</v>
       </c>
       <c r="Q22" t="n">
-        <v>3500</v>
+        <v>1246</v>
       </c>
       <c r="R22" t="n">
-        <v>-50000</v>
+        <v>-599000</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>미증시 제약바이오와는 다른 움직임, 탈모주 관련 기대감 있으나 구체적인 재료 및 공시 부재.</t>
+          <t>탈모 관련주로 언급되나 구체적인 재료 및 뉴스 부재, 하락 추세 및 조정 국면.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,11 +2475,11 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['탈모주', '재료']</t>
+          <t>['탈모주', '하락']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,77 +2488,77 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3740</v>
+        <v>10040</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-3.86%</t>
+          <t>-3.83%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.52</v>
+        <v>0.32</v>
       </c>
       <c r="E23" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="F23" t="n">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="G23" t="n">
-        <v>195</v>
+        <v>233</v>
       </c>
       <c r="H23" t="n">
-        <v>2.08</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>3890</v>
+        <v>10440</v>
       </c>
       <c r="K23" t="n">
-        <v>3890</v>
+        <v>10180</v>
       </c>
       <c r="L23" t="n">
-        <v>4115</v>
+        <v>11340</v>
       </c>
       <c r="M23" t="n">
-        <v>3700</v>
+        <v>9980</v>
       </c>
       <c r="N23" t="n">
-        <v>1.56</v>
+        <v>0.62</v>
       </c>
       <c r="O23" t="n">
-        <v>66503090377</v>
+        <v>146950594215</v>
       </c>
       <c r="P23" t="n">
-        <v>4335</v>
+        <v>15960</v>
       </c>
       <c r="Q23" t="n">
-        <v>1246</v>
+        <v>3500</v>
       </c>
       <c r="R23" t="n">
-        <v>-599000</v>
+        <v>-50000</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>탈모 관련주로 언급되나 구체적인 재료 및 뉴스 부재, 하락 추세 및 조정 국면.</t>
+          <t>미증시 제약바이오와는 다른 움직임, 탈모주 관련 기대감 있으나 구체적인 재료 및 공시 부재.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
@@ -2567,11 +2567,11 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['탈모주', '하락']</t>
+          <t>['탈모주', '재료']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>004310</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260909_14.xlsx
+++ b/data/trending_integrated_20260909_14.xlsx
@@ -578,13 +578,13 @@
         <v>-1.06</v>
       </c>
       <c r="E2" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F2" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G2" t="n">
-        <v>1564</v>
+        <v>1599</v>
       </c>
       <c r="H2" t="n">
         <v>0.77</v>
@@ -610,7 +610,7 @@
         <v>1.83</v>
       </c>
       <c r="O2" t="n">
-        <v>29737412175</v>
+        <v>29742101615</v>
       </c>
       <c r="P2" t="n">
         <v>21500</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미 FDA 2A상 승인 및 다락손라십 대비 우수한 효능 확인. 5연상 기대감 고조.</t>
+          <t>미 FDA 2A상 승인, 병용요법 연구 결과 공개, 암치료제 획기적 효능 기대.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['FDA', '암치료제', '효능']</t>
+          <t>['FDA', '암치료제']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>-0.08</v>
       </c>
       <c r="E3" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F3" t="n">
         <v>105</v>
       </c>
       <c r="G3" t="n">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="H3" t="n">
         <v>0.36</v>
@@ -702,7 +702,7 @@
         <v>0.44</v>
       </c>
       <c r="O3" t="n">
-        <v>233014216615</v>
+        <v>233176179515</v>
       </c>
       <c r="P3" t="n">
         <v>20850</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 증시 SMR 관련주 동반 급등 및 품절주 특징 부각. 신규 재료 기대감.</t>
+          <t>미국 증시 SMR 관련주 폭등, 가스터빈 대장, 물량 이슈.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['SMR', '품절주', '재료']</t>
+          <t>['SMR', '가스터빈']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -762,13 +762,13 @@
         <v>0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F4" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G4" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H4" t="n">
         <v>2.46</v>
@@ -794,7 +794,7 @@
         <v>2.45</v>
       </c>
       <c r="O4" t="n">
-        <v>37934650605</v>
+        <v>37946312355</v>
       </c>
       <c r="P4" t="n">
         <v>16200</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13930</v>
+        <v>13880</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+17.95%</t>
+          <t>+17.53%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.22</v>
       </c>
       <c r="E5" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F5" t="n">
         <v>163</v>
       </c>
       <c r="G5" t="n">
-        <v>1442</v>
+        <v>1456</v>
       </c>
       <c r="H5" t="n">
         <v>5.64</v>
@@ -886,7 +886,7 @@
         <v>5.42</v>
       </c>
       <c r="O5" t="n">
-        <v>477472931945</v>
+        <v>482707675585</v>
       </c>
       <c r="P5" t="n">
         <v>30200</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7190</v>
+        <v>7270</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+14.86%</t>
+          <t>+16.13%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F6" t="n">
         <v>112</v>
       </c>
       <c r="G6" t="n">
-        <v>1260</v>
+        <v>1274</v>
       </c>
       <c r="H6" t="n">
         <v>7.4</v>
@@ -978,7 +978,7 @@
         <v>7.35</v>
       </c>
       <c r="O6" t="n">
-        <v>69494672970</v>
+        <v>70094505380</v>
       </c>
       <c r="P6" t="n">
         <v>21500</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>53800</v>
+        <v>53700</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+9.24%</t>
+          <t>+9.04%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.03</v>
       </c>
       <c r="E7" t="n">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="F7" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="G7" t="n">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="H7" t="n">
         <v>14.96</v>
@@ -1070,7 +1070,7 @@
         <v>14.93</v>
       </c>
       <c r="O7" t="n">
-        <v>163034458000</v>
+        <v>163987257000</v>
       </c>
       <c r="P7" t="n">
         <v>108900</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14870</v>
+        <v>14910</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+8.54%</t>
+          <t>+8.83%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.39</v>
       </c>
       <c r="E8" t="n">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="F8" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G8" t="n">
-        <v>1423</v>
+        <v>1444</v>
       </c>
       <c r="H8" t="n">
         <v>1.55</v>
@@ -1162,7 +1162,7 @@
         <v>1.94</v>
       </c>
       <c r="O8" t="n">
-        <v>427323960390</v>
+        <v>432641911245</v>
       </c>
       <c r="P8" t="n">
         <v>31500</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6820</v>
+        <v>6810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+6.07%</t>
+          <t>+5.91%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.31</v>
       </c>
       <c r="E9" t="n">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="F9" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G9" t="n">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="H9" t="n">
         <v>16.71</v>
@@ -1254,7 +1254,7 @@
         <v>16.4</v>
       </c>
       <c r="O9" t="n">
-        <v>99305201865</v>
+        <v>99652661920</v>
       </c>
       <c r="P9" t="n">
         <v>13000</v>
@@ -1299,31 +1299,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31250</v>
+        <v>3805</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+5.04%</t>
+          <t>+4.53%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.08</v>
+        <v>2.74</v>
       </c>
       <c r="E10" t="n">
-        <v>694</v>
+        <v>230</v>
       </c>
       <c r="F10" t="n">
-        <v>251</v>
+        <v>128</v>
       </c>
       <c r="G10" t="n">
-        <v>993</v>
+        <v>523</v>
       </c>
       <c r="H10" t="n">
-        <v>0.31</v>
+        <v>3.19</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>29750</v>
+        <v>3640</v>
       </c>
       <c r="K10" t="n">
-        <v>31600</v>
+        <v>3750</v>
       </c>
       <c r="L10" t="n">
-        <v>34200</v>
+        <v>4460</v>
       </c>
       <c r="M10" t="n">
-        <v>28300</v>
+        <v>3680</v>
       </c>
       <c r="N10" t="n">
-        <v>0.23</v>
+        <v>0.45</v>
       </c>
       <c r="O10" t="n">
-        <v>508127145875</v>
+        <v>273965701912</v>
       </c>
       <c r="P10" t="n">
-        <v>39350</v>
+        <v>8100</v>
       </c>
       <c r="Q10" t="n">
-        <v>8200</v>
+        <v>592</v>
       </c>
       <c r="R10" t="n">
-        <v>-1000</v>
+        <v>-731000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>세계 최초 혈압 반지의 유럽 진출 뉴스 확인. 최저점 매수 논의 및 2차 파동 기대.</t>
+          <t>미국 광통신 폭등 관련, 6G 기반, 국책사업 선정 기대.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['혈압반지', '유럽진출', '최저점']</t>
+          <t>['광통신', '6G']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,130 +1384,130 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>써니전자</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2245</v>
+        <v>1998</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+3.94%</t>
+          <t>+3.95%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.23</v>
+        <v>-0.1</v>
       </c>
       <c r="E11" t="n">
-        <v>147</v>
+        <v>118</v>
       </c>
       <c r="F11" t="n">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="G11" t="n">
-        <v>314</v>
+        <v>286</v>
       </c>
       <c r="H11" t="n">
-        <v>5.26</v>
+        <v>0.51</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>2160</v>
+        <v>1922</v>
       </c>
       <c r="K11" t="n">
-        <v>2200</v>
+        <v>1920</v>
       </c>
       <c r="L11" t="n">
-        <v>2705</v>
+        <v>2165</v>
       </c>
       <c r="M11" t="n">
-        <v>2200</v>
+        <v>1862</v>
       </c>
       <c r="N11" t="n">
-        <v>5.49</v>
+        <v>0.61</v>
       </c>
       <c r="O11" t="n">
-        <v>41787657462</v>
+        <v>17347678072</v>
       </c>
       <c r="P11" t="n">
-        <v>2705</v>
+        <v>2930</v>
       </c>
       <c r="Q11" t="n">
-        <v>1418</v>
+        <v>910</v>
       </c>
       <c r="R11" t="n">
-        <v>22000</v>
+        <v>154000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>기타 법인 장내 매수세 유입 및 지분 싸움 기대감. 단기 과열 우려도 존재.</t>
+          <t>반도체 클러스터 관련주로 언급. 대주주 매도 공시 및 주가 하락 우려.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['PBR', '지분싸움', '기타법인']</t>
+          <t>['반도체 클러스터', '대주주 매도', '주가 전망']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>004770</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3780</v>
+        <v>30850</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+3.85%</t>
+          <t>+3.70%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2.74</v>
+        <v>0.08</v>
       </c>
       <c r="E12" t="n">
-        <v>229</v>
+        <v>705</v>
       </c>
       <c r="F12" t="n">
-        <v>127</v>
+        <v>250</v>
       </c>
       <c r="G12" t="n">
-        <v>514</v>
+        <v>1012</v>
       </c>
       <c r="H12" t="n">
-        <v>3.19</v>
+        <v>0.31</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>3640</v>
+        <v>29750</v>
       </c>
       <c r="K12" t="n">
-        <v>3750</v>
+        <v>31600</v>
       </c>
       <c r="L12" t="n">
-        <v>4460</v>
+        <v>34200</v>
       </c>
       <c r="M12" t="n">
-        <v>3680</v>
+        <v>28300</v>
       </c>
       <c r="N12" t="n">
-        <v>0.45</v>
+        <v>0.23</v>
       </c>
       <c r="O12" t="n">
-        <v>273083000735</v>
+        <v>516227295575</v>
       </c>
       <c r="P12" t="n">
-        <v>8100</v>
+        <v>39350</v>
       </c>
       <c r="Q12" t="n">
-        <v>592</v>
+        <v>8200</v>
       </c>
       <c r="R12" t="n">
-        <v>-731000</v>
+        <v>-1000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 광통신 산업 급등에 따른 기대감. 투기 과열 종목 지정 우려 및 6G 기반 성장성.</t>
+          <t>세계 최초 혈압 반지, 유럽 진출 뉴스, 1차 파동 조정 후 2차 파동 시작 기대.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['광통신', '6G', '투기과열']</t>
+          <t>['혈압 반지', '유럽 진출']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,130 +1568,130 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1986</v>
+        <v>1852000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+3.33%</t>
+          <t>+3.29%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.1</v>
+        <v>0.03</v>
       </c>
       <c r="E13" t="n">
-        <v>118</v>
+        <v>791</v>
       </c>
       <c r="F13" t="n">
-        <v>47</v>
+        <v>445</v>
       </c>
       <c r="G13" t="n">
-        <v>277</v>
+        <v>1692</v>
       </c>
       <c r="H13" t="n">
-        <v>0.51</v>
+        <v>50.66</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1922</v>
+        <v>1793000</v>
       </c>
       <c r="K13" t="n">
-        <v>1920</v>
+        <v>1795000</v>
       </c>
       <c r="L13" t="n">
-        <v>2165</v>
+        <v>1883000</v>
       </c>
       <c r="M13" t="n">
-        <v>1862</v>
+        <v>1795000</v>
       </c>
       <c r="N13" t="n">
-        <v>0.61</v>
+        <v>50.63</v>
       </c>
       <c r="O13" t="n">
-        <v>17132888371</v>
+        <v>5678214655000</v>
       </c>
       <c r="P13" t="n">
-        <v>2930</v>
+        <v>2987000</v>
       </c>
       <c r="Q13" t="n">
-        <v>910</v>
+        <v>277000</v>
       </c>
       <c r="R13" t="n">
-        <v>154000</v>
+        <v>180000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>151000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>반도체 클러스터 관련주로 언급. 대주주 매도 공시 및 주가 하락 우려.</t>
+          <t>상승 추세 전환 신호, 외인/기관 매수세 유입, 악성매물 소화.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['반도체 클러스터', '대주주 매도', '주가 전망']</t>
+          <t>['상승 추세', '외인 매수', '악성매물']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1851000</v>
+        <v>91800</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+3.23%</t>
+          <t>+2.57%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="E14" t="n">
-        <v>792</v>
+        <v>353</v>
       </c>
       <c r="F14" t="n">
-        <v>438</v>
+        <v>224</v>
       </c>
       <c r="G14" t="n">
-        <v>1711</v>
+        <v>1727</v>
       </c>
       <c r="H14" t="n">
-        <v>50.66</v>
+        <v>23.61</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1793000</v>
+        <v>89500</v>
       </c>
       <c r="K14" t="n">
-        <v>1795000</v>
+        <v>92000</v>
       </c>
       <c r="L14" t="n">
-        <v>1883000</v>
+        <v>94400</v>
       </c>
       <c r="M14" t="n">
-        <v>1795000</v>
+        <v>91100</v>
       </c>
       <c r="N14" t="n">
-        <v>50.63</v>
+        <v>23.63</v>
       </c>
       <c r="O14" t="n">
-        <v>5555893967500</v>
+        <v>314743516850</v>
       </c>
       <c r="P14" t="n">
-        <v>2987000</v>
+        <v>139200</v>
       </c>
       <c r="Q14" t="n">
-        <v>277000</v>
+        <v>57000</v>
       </c>
       <c r="R14" t="n">
-        <v>180000</v>
+        <v>123000</v>
       </c>
       <c r="S14" t="n">
-        <v>151000</v>
+        <v>96000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>외국인 및 기관의 지속적인 매수세 유입 확인. 상승 추세 전환 신호 및 악성 매물 소화 기대.</t>
+          <t>미국 원전주 급등 및 SMR 관련 긍정적 전망. 한-프랑스 정상회담 원자력 협력 기대감 반영. 하반기 주도주 가능성 및 대미 투자 수혜 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['외인매수', '상승추세', '악성매물']</t>
+          <t>['원전', 'SMR', '한-프랑스']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,90 +1752,90 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>서산</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>91600</v>
+        <v>7860</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+2.35%</t>
+          <t>+2.34%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.02</v>
+        <v>1.4</v>
       </c>
       <c r="E15" t="n">
-        <v>348</v>
+        <v>143</v>
       </c>
       <c r="F15" t="n">
-        <v>221</v>
+        <v>85</v>
       </c>
       <c r="G15" t="n">
-        <v>1711</v>
+        <v>381</v>
       </c>
       <c r="H15" t="n">
-        <v>23.61</v>
+        <v>1.81</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>89500</v>
+        <v>7680</v>
       </c>
       <c r="K15" t="n">
-        <v>92000</v>
+        <v>7780</v>
       </c>
       <c r="L15" t="n">
-        <v>94400</v>
+        <v>9000</v>
       </c>
       <c r="M15" t="n">
-        <v>91100</v>
+        <v>7690</v>
       </c>
       <c r="N15" t="n">
-        <v>23.63</v>
+        <v>0.41</v>
       </c>
       <c r="O15" t="n">
-        <v>309774192850</v>
+        <v>118313720035</v>
       </c>
       <c r="P15" t="n">
-        <v>139200</v>
+        <v>10300</v>
       </c>
       <c r="Q15" t="n">
-        <v>57000</v>
+        <v>952</v>
       </c>
       <c r="R15" t="n">
-        <v>123000</v>
+        <v>-211000</v>
       </c>
       <c r="S15" t="n">
-        <v>96000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 원전주 급등 및 SMR 관련 긍정적 전망. 한-프랑스 정상회담 원자력 협력 기대감 반영. 하반기 주도주 가능성 및 대미 투자 수혜 언급.</t>
+          <t>레미콘 파업 시작 및 대장주로서의 강세 기대. 하지만 전반적인 상승 동력은 약함.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '한-프랑스']</t>
+          <t>['레미콘', '대장주', '파업']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,77 +1844,77 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>079650</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>서산</t>
+          <t>써니전자</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7730</v>
+        <v>2180</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+0.65%</t>
+          <t>+0.93%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.4</v>
+        <v>-0.23</v>
       </c>
       <c r="E16" t="n">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="F16" t="n">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="G16" t="n">
-        <v>378</v>
+        <v>348</v>
       </c>
       <c r="H16" t="n">
-        <v>1.81</v>
+        <v>5.26</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>7680</v>
+        <v>2160</v>
       </c>
       <c r="K16" t="n">
-        <v>7780</v>
+        <v>2200</v>
       </c>
       <c r="L16" t="n">
-        <v>9000</v>
+        <v>2705</v>
       </c>
       <c r="M16" t="n">
-        <v>7690</v>
+        <v>2180</v>
       </c>
       <c r="N16" t="n">
-        <v>0.41</v>
+        <v>5.49</v>
       </c>
       <c r="O16" t="n">
-        <v>117384898455</v>
+        <v>43156761833</v>
       </c>
       <c r="P16" t="n">
-        <v>10300</v>
+        <v>2705</v>
       </c>
       <c r="Q16" t="n">
-        <v>952</v>
+        <v>1418</v>
       </c>
       <c r="R16" t="n">
-        <v>-211000</v>
+        <v>22000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>레미콘 파업 시작 및 대장주로서의 강세 기대. 하지만 전반적인 상승 동력은 약함.</t>
+          <t>지분 싸움 및 기타법인 장내매수, 단기 목표가 설정.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['레미콘', '대장주', '파업']</t>
+          <t>['지분 싸움', '장내매수']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>079650</t>
+          <t>004770</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12050</v>
+        <v>12070</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+0.50%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-2.16</v>
       </c>
       <c r="E17" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="F17" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G17" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1990,7 +1990,7 @@
         <v>2.16</v>
       </c>
       <c r="O17" t="n">
-        <v>46532096305</v>
+        <v>47867563250</v>
       </c>
       <c r="P17" t="n">
         <v>36200</v>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8945</v>
+        <v>8980</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.45%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.36</v>
       </c>
       <c r="E18" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F18" t="n">
         <v>68</v>
       </c>
       <c r="G18" t="n">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="H18" t="n">
         <v>27.69</v>
@@ -2082,7 +2082,7 @@
         <v>28.05</v>
       </c>
       <c r="O18" t="n">
-        <v>31730490160</v>
+        <v>32684986350</v>
       </c>
       <c r="P18" t="n">
         <v>17950</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>AI 관련 기대감 있으나, 개인 투자자 매수 집중 및 기업 성장성 의문 제기.</t>
+          <t>매도, 중국산 영향, 개인 매수 집중 등 부정적 전망.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['AI', '개인투자자', '성장성']</t>
+          <t>['매도', '중국산']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>268750</v>
+        <v>269500</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.06</v>
       </c>
       <c r="E19" t="n">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="F19" t="n">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="G19" t="n">
-        <v>1770</v>
+        <v>1712</v>
       </c>
       <c r="H19" t="n">
         <v>46.85</v>
@@ -2174,7 +2174,7 @@
         <v>46.79</v>
       </c>
       <c r="O19" t="n">
-        <v>3672169233250</v>
+        <v>3766183064250</v>
       </c>
       <c r="P19" t="n">
         <v>374500</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>하이닉스와의 주가 비교 열세 및 경영진에 대한 부정적 의견 대두.</t>
+          <t>노조, 이재용 해임, 하이닉스와의 비교 등 부정적 언급.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['하이닉스', '주가', '경영진']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,11 +2223,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>33625</v>
+        <v>33700</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.39%</t>
+          <t>-1.17%</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2237,13 +2237,13 @@
         <v>132</v>
       </c>
       <c r="F20" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G20" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H20" t="n">
-        <v>52.57</v>
+        <v>52.56</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>21.01</v>
       </c>
       <c r="O20" t="n">
-        <v>82740620325</v>
+        <v>84099487100</v>
       </c>
       <c r="P20" t="n">
         <v>69500</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>한국-프랑스 차세대 원전 협력 뉴스 및 25조 선납매 논의. 공매도 세력의 움직임 주시.</t>
+          <t>미국 원전 협력, 공매도 이슈, SMP 급락 우려.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['원전', '선납매', '공매도']</t>
+          <t>['원전', '공매도']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19420</v>
+        <v>19540</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.75%</t>
+          <t>-2.15%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.38</v>
       </c>
       <c r="E21" t="n">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="F21" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G21" t="n">
-        <v>753</v>
+        <v>758</v>
       </c>
       <c r="H21" t="n">
         <v>10.85</v>
@@ -2358,7 +2358,7 @@
         <v>10.47</v>
       </c>
       <c r="O21" t="n">
-        <v>276765273045</v>
+        <v>280620347755</v>
       </c>
       <c r="P21" t="n">
         <v>40350</v>
@@ -2418,13 +2418,13 @@
         <v>0.52</v>
       </c>
       <c r="E22" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F22" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G22" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H22" t="n">
         <v>2.08</v>
@@ -2450,7 +2450,7 @@
         <v>1.56</v>
       </c>
       <c r="O22" t="n">
-        <v>66740430704</v>
+        <v>66962221584</v>
       </c>
       <c r="P22" t="n">
         <v>4335</v>
@@ -2499,11 +2499,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10040</v>
+        <v>10060</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-3.83%</t>
+          <t>-3.64%</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -2516,7 +2516,7 @@
         <v>72</v>
       </c>
       <c r="G23" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H23" t="n">
         <v>0.9399999999999999</v>
@@ -2542,7 +2542,7 @@
         <v>0.62</v>
       </c>
       <c r="O23" t="n">
-        <v>146950594215</v>
+        <v>147390691635</v>
       </c>
       <c r="P23" t="n">
         <v>15960</v>
